--- a/artfynd/A 26008-2026 artfynd.xlsx
+++ b/artfynd/A 26008-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>85933704</v>
+        <v>5226609</v>
       </c>
       <c r="B2" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,26 +703,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Laggarån, SV om Laggartorp, Srm</t>
+          <t>BÄCK SÖDER LAGGARTORP (10G5j11), Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592302.7021698389</v>
+        <v>592410</v>
       </c>
       <c r="R2" t="n">
-        <v>6576928.686061861</v>
+        <v>6576897</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-05-31</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1994-09-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-05-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1994-09-30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>100659111 / ACTA SPI / Allmän-riklig (3)  / AJO / OBJ.AREA:0,6 ha</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,36 +761,30 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Lövskog, vid bäck</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>85933685</v>
+        <v>85933679</v>
       </c>
       <c r="B3" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,7 +811,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592212.4863293676</v>
+        <v>592192</v>
       </c>
       <c r="R3" t="n">
-        <v>6576957.636685246</v>
+        <v>6576967</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,19 +858,9 @@
           <t>2020-05-31</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-05-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,15 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>85933703</v>
+        <v>85933683</v>
       </c>
       <c r="B4" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,7 +922,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -976,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592262.5683700844</v>
+        <v>592202</v>
       </c>
       <c r="R4" t="n">
-        <v>6576938.431539575</v>
+        <v>6576968</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,19 +969,9 @@
           <t>2020-05-31</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-05-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,15 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>85933712</v>
+        <v>85933685</v>
       </c>
       <c r="B5" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1033,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1102,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592312.6633640146</v>
+        <v>592212</v>
       </c>
       <c r="R5" t="n">
-        <v>6576918.716643807</v>
+        <v>6576958</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,19 +1080,9 @@
           <t>2020-05-31</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-05-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1182,12 +1117,7 @@
         <v>85933690</v>
       </c>
       <c r="B6" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592232.6440517229</v>
+        <v>592233</v>
       </c>
       <c r="R6" t="n">
-        <v>6576928.001925118</v>
+        <v>6576928</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1261,19 +1191,9 @@
           <t>2020-05-31</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-05-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,6 +1222,339 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>85933703</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Laggarån, SV om Laggartorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>592263</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6576938</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-05-31</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-05-31</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Lövskog, vid bäck</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>85933704</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Laggarån, SV om Laggartorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>592303</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6576929</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-05-31</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-05-31</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Lövskog, vid bäck</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>85933712</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Laggarån, SV om Laggartorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>592313</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6576919</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-05-31</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-05-31</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Lövskog, vid bäck</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26008-2026 artfynd.xlsx
+++ b/artfynd/A 26008-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5226609</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85933679</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85933683</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85933685</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85933690</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1333,6 +1363,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85933703</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1444,6 +1479,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85933704</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1555,8 +1595,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85933712</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>